--- a/internal/repository/idl/student.xlsx
+++ b/internal/repository/idl/student.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14462" windowHeight="6786"/>
+    <workbookView windowWidth="27645" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="STUDENT" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t>列名</t>
   </si>
@@ -71,6 +71,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>///@omitempty</t>
+  </si>
+  <si>
     <t>AGE</t>
   </si>
   <si>
@@ -119,7 +122,7 @@
     <t>索引</t>
   </si>
   <si>
-    <t>INDEX_NAME_AGE</t>
+    <t>INDEX_AGE</t>
   </si>
   <si>
     <t>自定义脚本名字</t>
@@ -158,16 +161,16 @@
     <t>ID,STUNO,NAME,AGE</t>
   </si>
   <si>
+    <t>AGE = @Age AND STUNO &gt; @Stuno</t>
+  </si>
+  <si>
+    <t>FindByAgeWithPage</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>AGE = @Age</t>
-  </si>
-  <si>
-    <t>FindByAgeWithPage</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>&gt;</t>
@@ -1267,17 +1270,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="67.624" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.376" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.4083333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.744" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.744" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.816" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8166666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1359,14 +1362,16 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
@@ -1375,13 +1380,13 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1397,43 +1402,43 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1445,7 +1450,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
@@ -1453,12 +1458,12 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:1">
       <c r="A13" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
@@ -1467,67 +1472,64 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:1">
       <c r="A16" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
       <c r="A20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:9">
       <c r="A21" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
       <c r="E21" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -1536,20 +1538,20 @@
     </row>
     <row r="22" customFormat="1" spans="1:9">
       <c r="A22" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
       <c r="E22" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="I22" s="11"/>
     </row>
@@ -1574,37 +1576,37 @@
     <row r="39" customFormat="1"/>
     <row r="49" s="1" customFormat="1" spans="5:5">
       <c r="E49" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="5:5">
       <c r="E50" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="5:5">
       <c r="E51" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="5:5">
       <c r="E52" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="5:5">
       <c r="E53" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="5:5">
       <c r="E54" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="5:5">
       <c r="E55" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
